--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/145.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/145.xlsx
@@ -426,13 +426,13 @@
         <v>-12.96517743056081</v>
       </c>
       <c r="E2">
-        <v>-17.2690976958361</v>
+        <v>-16.50367690516363</v>
       </c>
       <c r="F2">
-        <v>-5.709196094286397</v>
+        <v>-5.992589694825539</v>
       </c>
       <c r="G2">
-        <v>-15.23930758532351</v>
+        <v>-13.98102638231843</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.78276690124033</v>
       </c>
       <c r="E3">
-        <v>-18.18538912654812</v>
+        <v>-16.57812954632374</v>
       </c>
       <c r="F3">
-        <v>-5.749272509233838</v>
+        <v>-5.550713671150199</v>
       </c>
       <c r="G3">
-        <v>-14.99988341057395</v>
+        <v>-13.81459790299106</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.62134618736902</v>
       </c>
       <c r="E4">
-        <v>-18.09719256677474</v>
+        <v>-18.19090480788947</v>
       </c>
       <c r="F4">
-        <v>-5.304305846778652</v>
+        <v>-5.667069470017029</v>
       </c>
       <c r="G4">
-        <v>-14.68942899211631</v>
+        <v>-13.39667199418614</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.50898674602992</v>
       </c>
       <c r="E5">
-        <v>-18.74745426343215</v>
+        <v>-18.54512657324345</v>
       </c>
       <c r="F5">
-        <v>-5.382864069423143</v>
+        <v>-5.96976734451101</v>
       </c>
       <c r="G5">
-        <v>-15.20496139865003</v>
+        <v>-13.21678886585427</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.41459123444397</v>
       </c>
       <c r="E6">
-        <v>-19.93557187492859</v>
+        <v>-18.28574463903211</v>
       </c>
       <c r="F6">
-        <v>-5.441990449532764</v>
+        <v>-5.961230190057758</v>
       </c>
       <c r="G6">
-        <v>-15.58390475471796</v>
+        <v>-13.87561549911049</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.32869051585062</v>
       </c>
       <c r="E7">
-        <v>-20.35377644953695</v>
+        <v>-18.01782653131631</v>
       </c>
       <c r="F7">
-        <v>-5.305023212949476</v>
+        <v>-6.024454503709028</v>
       </c>
       <c r="G7">
-        <v>-15.57447452395611</v>
+        <v>-12.95147913422224</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.23031953152714</v>
       </c>
       <c r="E8">
-        <v>-20.72988885824401</v>
+        <v>-18.19532459852095</v>
       </c>
       <c r="F8">
-        <v>-5.209676468152447</v>
+        <v>-5.637331080256526</v>
       </c>
       <c r="G8">
-        <v>-14.86280381748503</v>
+        <v>-13.51098319087408</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.09621259032823</v>
       </c>
       <c r="E9">
-        <v>-20.72024773708168</v>
+        <v>-20.43282549181485</v>
       </c>
       <c r="F9">
-        <v>-5.260531599745115</v>
+        <v>-5.143945514740307</v>
       </c>
       <c r="G9">
-        <v>-14.77096406664695</v>
+        <v>-12.57288522825039</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.91378448880405</v>
       </c>
       <c r="E10">
-        <v>-21.20444576340382</v>
+        <v>-21.11185658384299</v>
       </c>
       <c r="F10">
-        <v>-5.104282455126864</v>
+        <v>-5.258644578801538</v>
       </c>
       <c r="G10">
-        <v>-14.49886712821922</v>
+        <v>-12.66978954456548</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.65701174680114</v>
       </c>
       <c r="E11">
-        <v>-22.65748816129699</v>
+        <v>-19.67262150319921</v>
       </c>
       <c r="F11">
-        <v>-5.243876444744428</v>
+        <v>-5.088105268117593</v>
       </c>
       <c r="G11">
-        <v>-14.27277127544412</v>
+        <v>-13.19392531402806</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.33583621815943</v>
       </c>
       <c r="E12">
-        <v>-23.16229527282804</v>
+        <v>-22.31751750364515</v>
       </c>
       <c r="F12">
-        <v>-5.190005227438168</v>
+        <v>-5.270293909587108</v>
       </c>
       <c r="G12">
-        <v>-14.00741888793183</v>
+        <v>-12.23343301426116</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.94478393793406</v>
       </c>
       <c r="E13">
-        <v>-23.21441348018232</v>
+        <v>-22.75694703592746</v>
       </c>
       <c r="F13">
-        <v>-5.209857052246258</v>
+        <v>-5.243475514921474</v>
       </c>
       <c r="G13">
-        <v>-13.51621017681827</v>
+        <v>-11.96843827989885</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.52438430673498</v>
       </c>
       <c r="E14">
-        <v>-24.66926726767856</v>
+        <v>-23.99676170669546</v>
       </c>
       <c r="F14">
-        <v>-4.714944805606679</v>
+        <v>-4.994454191394095</v>
       </c>
       <c r="G14">
-        <v>-13.54735225063896</v>
+        <v>-10.40954632311446</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.10386405769354</v>
       </c>
       <c r="E15">
-        <v>-24.79399955574583</v>
+        <v>-25.2071956381017</v>
       </c>
       <c r="F15">
-        <v>-4.758476340991196</v>
+        <v>-5.007193653681748</v>
       </c>
       <c r="G15">
-        <v>-12.99697983358706</v>
+        <v>-11.20306710138589</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.729596154542282</v>
       </c>
       <c r="E16">
-        <v>-24.86600229246779</v>
+        <v>-24.82544075078108</v>
       </c>
       <c r="F16">
-        <v>-4.653251314915783</v>
+        <v>-4.750340116360899</v>
       </c>
       <c r="G16">
-        <v>-12.6722471795135</v>
+        <v>-10.40041468351452</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.431994379260498</v>
       </c>
       <c r="E17">
-        <v>-25.74901396769744</v>
+        <v>-26.55797603595366</v>
       </c>
       <c r="F17">
-        <v>-4.4479329988253</v>
+        <v>-4.050309190174913</v>
       </c>
       <c r="G17">
-        <v>-12.2662616359634</v>
+        <v>-10.70268409479213</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.224737591794119</v>
       </c>
       <c r="E18">
-        <v>-26.91987356475065</v>
+        <v>-27.08112799568978</v>
       </c>
       <c r="F18">
-        <v>-4.150998076352596</v>
+        <v>-4.023021939559294</v>
       </c>
       <c r="G18">
-        <v>-11.31052054501458</v>
+        <v>-10.11139812611551</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.116294698995997</v>
       </c>
       <c r="E19">
-        <v>-27.14856603061201</v>
+        <v>-25.90590294969318</v>
       </c>
       <c r="F19">
-        <v>-3.899204207128047</v>
+        <v>-3.954661748010668</v>
       </c>
       <c r="G19">
-        <v>-11.88768413609935</v>
+        <v>-11.52957817754467</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.083561815246194</v>
       </c>
       <c r="E20">
-        <v>-28.015836730191</v>
+        <v>-26.73353138780902</v>
       </c>
       <c r="F20">
-        <v>-3.721796073940088</v>
+        <v>-3.991868698274811</v>
       </c>
       <c r="G20">
-        <v>-11.52146699784973</v>
+        <v>-10.50804531310743</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.117017662077698</v>
       </c>
       <c r="E21">
-        <v>-28.27660890592269</v>
+        <v>-27.93470458986958</v>
       </c>
       <c r="F21">
-        <v>-3.588916002122213</v>
+        <v>-3.554096406712939</v>
       </c>
       <c r="G21">
-        <v>-11.28570138513895</v>
+        <v>-9.308237118902435</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.173551549865048</v>
       </c>
       <c r="E22">
-        <v>-29.33325133155444</v>
+        <v>-29.4255620099638</v>
       </c>
       <c r="F22">
-        <v>-3.517685517522887</v>
+        <v>-3.422799345001815</v>
       </c>
       <c r="G22">
-        <v>-11.85038649063314</v>
+        <v>-9.41249137151067</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.235227380571242</v>
       </c>
       <c r="E23">
-        <v>-29.74578172823119</v>
+        <v>-28.68010952542815</v>
       </c>
       <c r="F23">
-        <v>-3.370578235561931</v>
+        <v>-3.153085403752504</v>
       </c>
       <c r="G23">
-        <v>-10.98283479153752</v>
+        <v>-10.57680331088559</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.264861212014646</v>
       </c>
       <c r="E24">
-        <v>-30.4542501655462</v>
+        <v>-28.91549960434685</v>
       </c>
       <c r="F24">
-        <v>-3.311174352372373</v>
+        <v>-2.904489861070164</v>
       </c>
       <c r="G24">
-        <v>-11.51998716692642</v>
+        <v>-9.55148063554719</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.246535284901634</v>
       </c>
       <c r="E25">
-        <v>-30.5255124967679</v>
+        <v>-30.71530537090337</v>
       </c>
       <c r="F25">
-        <v>-3.230816915729001</v>
+        <v>-2.882203464465246</v>
       </c>
       <c r="G25">
-        <v>-11.06649937886024</v>
+        <v>-10.26688537215292</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.166441179581275</v>
       </c>
       <c r="E26">
-        <v>-30.14761586930182</v>
+        <v>-29.45177961023121</v>
       </c>
       <c r="F26">
-        <v>-3.159297330906097</v>
+        <v>-2.955387239400374</v>
       </c>
       <c r="G26">
-        <v>-11.63835395346183</v>
+        <v>-9.899782304082246</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.020775585471124</v>
       </c>
       <c r="E27">
-        <v>-30.52213878363219</v>
+        <v>-30.00188957573499</v>
       </c>
       <c r="F27">
-        <v>-3.008007621928407</v>
+        <v>-2.889763145383194</v>
       </c>
       <c r="G27">
-        <v>-10.74936275269679</v>
+        <v>-10.73964377443771</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.82027920500466</v>
       </c>
       <c r="E28">
-        <v>-30.82118109320271</v>
+        <v>-29.4755722126675</v>
       </c>
       <c r="F28">
-        <v>-2.911916174836262</v>
+        <v>-3.257681698969192</v>
       </c>
       <c r="G28">
-        <v>-11.30334779468564</v>
+        <v>-9.585625027094771</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.567400979028747</v>
       </c>
       <c r="E29">
-        <v>-29.89533005386049</v>
+        <v>-29.29407550291409</v>
       </c>
       <c r="F29">
-        <v>-3.356713021973873</v>
+        <v>-2.962012521887964</v>
       </c>
       <c r="G29">
-        <v>-11.42590470115246</v>
+        <v>-10.16000614229713</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.287423652261968</v>
       </c>
       <c r="E30">
-        <v>-29.7399445252353</v>
+        <v>-30.45280331810075</v>
       </c>
       <c r="F30">
-        <v>-3.107091132079464</v>
+        <v>-3.101435867820552</v>
       </c>
       <c r="G30">
-        <v>-11.02858814496242</v>
+        <v>-10.22248060078896</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.986330521530967</v>
       </c>
       <c r="E31">
-        <v>-30.33728194616507</v>
+        <v>-28.1414158428977</v>
       </c>
       <c r="F31">
-        <v>-3.267280820432833</v>
+        <v>-3.027589398963185</v>
       </c>
       <c r="G31">
-        <v>-11.40019633023421</v>
+        <v>-10.05399643615459</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.690407913826142</v>
       </c>
       <c r="E32">
-        <v>-29.58966258681675</v>
+        <v>-29.2954385735904</v>
       </c>
       <c r="F32">
-        <v>-3.282059723266178</v>
+        <v>-2.775061596219755</v>
       </c>
       <c r="G32">
-        <v>-11.37614497620348</v>
+        <v>-10.21484847944169</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.405669029859785</v>
       </c>
       <c r="E33">
-        <v>-29.9011197078793</v>
+        <v>-29.21372678859599</v>
       </c>
       <c r="F33">
-        <v>-3.342681306537852</v>
+        <v>-2.991784874711982</v>
       </c>
       <c r="G33">
-        <v>-11.55839058405816</v>
+        <v>-10.32488096321611</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.149260421248483</v>
       </c>
       <c r="E34">
-        <v>-29.38864362561626</v>
+        <v>-28.96952882773237</v>
       </c>
       <c r="F34">
-        <v>-3.212955657789838</v>
+        <v>-2.973350386530081</v>
       </c>
       <c r="G34">
-        <v>-11.45012995992584</v>
+        <v>-9.658852048636899</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.929177586898433</v>
       </c>
       <c r="E35">
-        <v>-29.35978366076538</v>
+        <v>-27.34053257227116</v>
       </c>
       <c r="F35">
-        <v>-3.011574571964862</v>
+        <v>-3.374561026034591</v>
       </c>
       <c r="G35">
-        <v>-11.22127459981925</v>
+        <v>-9.587085170688724</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.751100386257055</v>
       </c>
       <c r="E36">
-        <v>-28.99775027774817</v>
+        <v>-28.75703471339644</v>
       </c>
       <c r="F36">
-        <v>-3.228810609879421</v>
+        <v>-3.313723238870787</v>
       </c>
       <c r="G36">
-        <v>-11.1715772180799</v>
+        <v>-10.30942312844956</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.623353170928447</v>
       </c>
       <c r="E37">
-        <v>-28.18660548502024</v>
+        <v>-29.37928779831642</v>
       </c>
       <c r="F37">
-        <v>-3.279516635339584</v>
+        <v>-2.941338956616297</v>
       </c>
       <c r="G37">
-        <v>-11.15430158656942</v>
+        <v>-8.604454469060256</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.539671696124762</v>
       </c>
       <c r="E38">
-        <v>-27.78857073364205</v>
+        <v>-27.91478383270983</v>
       </c>
       <c r="F38">
-        <v>-3.24167018544048</v>
+        <v>-3.324391782651442</v>
       </c>
       <c r="G38">
-        <v>-11.30929993059447</v>
+        <v>-9.321870594481927</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.509562966270246</v>
       </c>
       <c r="E39">
-        <v>-27.89239505721591</v>
+        <v>-26.95577077820945</v>
       </c>
       <c r="F39">
-        <v>-3.240614845369314</v>
+        <v>-3.010389178211455</v>
       </c>
       <c r="G39">
-        <v>-11.13131991076707</v>
+        <v>-8.452839064462994</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.519998244976148</v>
       </c>
       <c r="E40">
-        <v>-28.02547332287932</v>
+        <v>-28.04933838089974</v>
       </c>
       <c r="F40">
-        <v>-2.947256813341897</v>
+        <v>-3.125439470051473</v>
       </c>
       <c r="G40">
-        <v>-10.80203620239056</v>
+        <v>-9.336839527236114</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.579475139253356</v>
       </c>
       <c r="E41">
-        <v>-26.86261553939766</v>
+        <v>-26.32258142856095</v>
       </c>
       <c r="F41">
-        <v>-3.283522620099522</v>
+        <v>-3.364918829466005</v>
       </c>
       <c r="G41">
-        <v>-11.01022314789421</v>
+        <v>-8.143026124820224</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.67640777967454</v>
       </c>
       <c r="E42">
-        <v>-26.39200746357254</v>
+        <v>-26.56531216384609</v>
       </c>
       <c r="F42">
-        <v>-3.139578044882455</v>
+        <v>-3.228999477647259</v>
       </c>
       <c r="G42">
-        <v>-10.87907600338476</v>
+        <v>-8.665695188245731</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.810456620362374</v>
       </c>
       <c r="E43">
-        <v>-25.66195405489998</v>
+        <v>-25.61688668157564</v>
       </c>
       <c r="F43">
-        <v>-3.299515909545372</v>
+        <v>-3.211179638078236</v>
       </c>
       <c r="G43">
-        <v>-10.30200756772522</v>
+        <v>-10.39476441998916</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.968766340022825</v>
       </c>
       <c r="E44">
-        <v>-26.08345535858592</v>
+        <v>-25.87258243794474</v>
       </c>
       <c r="F44">
-        <v>-3.340137390243854</v>
+        <v>-3.521391633283012</v>
       </c>
       <c r="G44">
-        <v>-10.62565085624105</v>
+        <v>-8.855179170860545</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.139945040890541</v>
       </c>
       <c r="E45">
-        <v>-25.53508885557509</v>
+        <v>-24.32583685588485</v>
       </c>
       <c r="F45">
-        <v>-3.376468756163238</v>
+        <v>-3.194391115925698</v>
       </c>
       <c r="G45">
-        <v>-11.22278068051503</v>
+        <v>-9.459035499331394</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.319409898376115</v>
       </c>
       <c r="E46">
-        <v>-25.22858814931394</v>
+        <v>-24.46924909923376</v>
       </c>
       <c r="F46">
-        <v>-3.279698047800797</v>
+        <v>-3.282991636594328</v>
       </c>
       <c r="G46">
-        <v>-10.89411056057014</v>
+        <v>-8.74719416933922</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.494723453777403</v>
       </c>
       <c r="E47">
-        <v>-25.22206714674289</v>
+        <v>-24.63345156675189</v>
       </c>
       <c r="F47">
-        <v>-3.305210935439619</v>
+        <v>-3.90261708082758</v>
       </c>
       <c r="G47">
-        <v>-10.82144790913623</v>
+        <v>-10.41357894441102</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.670404901432019</v>
       </c>
       <c r="E48">
-        <v>-24.09534658584245</v>
+        <v>-24.59612335550667</v>
       </c>
       <c r="F48">
-        <v>-3.575006885061807</v>
+        <v>-3.493116140355853</v>
       </c>
       <c r="G48">
-        <v>-11.03894039898247</v>
+        <v>-9.159282784989882</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.832959759264607</v>
       </c>
       <c r="E49">
-        <v>-24.10969279149874</v>
+        <v>-23.36425162814811</v>
       </c>
       <c r="F49">
-        <v>-3.505695727734767</v>
+        <v>-3.764325284767217</v>
       </c>
       <c r="G49">
-        <v>-10.98550242466535</v>
+        <v>-9.146016806225047</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.992085536365961</v>
       </c>
       <c r="E50">
-        <v>-23.51234631362096</v>
+        <v>-23.10208015394804</v>
       </c>
       <c r="F50">
-        <v>-3.373991109261465</v>
+        <v>-3.881757132890284</v>
       </c>
       <c r="G50">
-        <v>-11.28120611160251</v>
+        <v>-10.44805145811454</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.139971373084679</v>
       </c>
       <c r="E51">
-        <v>-23.78035951929092</v>
+        <v>-23.23058918933771</v>
       </c>
       <c r="F51">
-        <v>-3.29060267629125</v>
+        <v>-3.921488946998159</v>
       </c>
       <c r="G51">
-        <v>-10.87501713231573</v>
+        <v>-9.88954489281678</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.28496738400249</v>
       </c>
       <c r="E52">
-        <v>-22.93445416008012</v>
+        <v>-23.32278892013388</v>
       </c>
       <c r="F52">
-        <v>-3.613981571363523</v>
+        <v>-3.97128873851966</v>
       </c>
       <c r="G52">
-        <v>-11.28292875292122</v>
+        <v>-9.156592183311137</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.426599269369204</v>
       </c>
       <c r="E53">
-        <v>-21.97403275016335</v>
+        <v>-22.89319523339623</v>
       </c>
       <c r="F53">
-        <v>-3.482325826566987</v>
+        <v>-3.556538433816392</v>
       </c>
       <c r="G53">
-        <v>-10.95712970184083</v>
+        <v>-8.807306148308246</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.567842432035498</v>
       </c>
       <c r="E54">
-        <v>-22.0498077057337</v>
+        <v>-22.32159765872606</v>
       </c>
       <c r="F54">
-        <v>-3.488435864530036</v>
+        <v>-4.081224690014793</v>
       </c>
       <c r="G54">
-        <v>-10.94800134346245</v>
+        <v>-8.900965336501036</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.714442362685517</v>
       </c>
       <c r="E55">
-        <v>-21.07462347055193</v>
+        <v>-22.15183875360052</v>
       </c>
       <c r="F55">
-        <v>-3.584913330831886</v>
+        <v>-4.007018709704611</v>
       </c>
       <c r="G55">
-        <v>-11.35349470377863</v>
+        <v>-8.682042234054885</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.861449690754107</v>
       </c>
       <c r="E56">
-        <v>-21.06273169780778</v>
+        <v>-20.31940080334473</v>
       </c>
       <c r="F56">
-        <v>-3.838725103049655</v>
+        <v>-3.91305036826584</v>
       </c>
       <c r="G56">
-        <v>-10.99151034134069</v>
+        <v>-8.840538360262302</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.019347859519733</v>
       </c>
       <c r="E57">
-        <v>-21.27691493294857</v>
+        <v>-21.01861077555105</v>
       </c>
       <c r="F57">
-        <v>-3.399480802613009</v>
+        <v>-3.706706533330692</v>
       </c>
       <c r="G57">
-        <v>-11.01999790691979</v>
+        <v>-9.851374442415759</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.175931404644441</v>
       </c>
       <c r="E58">
-        <v>-20.47623544365237</v>
+        <v>-19.86806138442224</v>
       </c>
       <c r="F58">
-        <v>-3.444651677087665</v>
+        <v>-3.779352697821403</v>
       </c>
       <c r="G58">
-        <v>-11.69007913012491</v>
+        <v>-9.39914336220685</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.342006283700192</v>
       </c>
       <c r="E59">
-        <v>-20.63745364679945</v>
+        <v>-20.06005962539945</v>
       </c>
       <c r="F59">
-        <v>-3.643666945610247</v>
+        <v>-3.440019446571211</v>
       </c>
       <c r="G59">
-        <v>-11.49882985031112</v>
+        <v>-9.589943114667001</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.504365704355559</v>
       </c>
       <c r="E60">
-        <v>-20.27104575789082</v>
+        <v>-21.10693866107066</v>
       </c>
       <c r="F60">
-        <v>-3.450461017683498</v>
+        <v>-3.396686719363366</v>
       </c>
       <c r="G60">
-        <v>-11.65648270257776</v>
+        <v>-10.46441162880993</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.666955500283978</v>
       </c>
       <c r="E61">
-        <v>-19.45917188084767</v>
+        <v>-20.45788153849929</v>
       </c>
       <c r="F61">
-        <v>-3.643292523544182</v>
+        <v>-3.930729385376388</v>
       </c>
       <c r="G61">
-        <v>-12.09859449549734</v>
+        <v>-9.7084805247235</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.821568939318256</v>
       </c>
       <c r="E62">
-        <v>-19.26422560329146</v>
+        <v>-19.73765491842336</v>
       </c>
       <c r="F62">
-        <v>-3.4302811593839</v>
+        <v>-3.726042285246838</v>
       </c>
       <c r="G62">
-        <v>-12.23413191445332</v>
+        <v>-9.872187230767317</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.965488576021219</v>
       </c>
       <c r="E63">
-        <v>-19.77744661952876</v>
+        <v>-19.66191166217107</v>
       </c>
       <c r="F63">
-        <v>-3.48178821612257</v>
+        <v>-3.624137355721845</v>
       </c>
       <c r="G63">
-        <v>-12.5002947636908</v>
+        <v>-9.719748239558633</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.09937123190372</v>
       </c>
       <c r="E64">
-        <v>-19.18251381829706</v>
+        <v>-19.49193991876717</v>
       </c>
       <c r="F64">
-        <v>-3.300895141271034</v>
+        <v>-3.322091406373867</v>
       </c>
       <c r="G64">
-        <v>-12.30122633290085</v>
+        <v>-9.773054965013372</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.2151559668394</v>
       </c>
       <c r="E65">
-        <v>-19.47464567653187</v>
+        <v>-19.56610726606479</v>
       </c>
       <c r="F65">
-        <v>-3.549891613776329</v>
+        <v>-3.49729028369856</v>
       </c>
       <c r="G65">
-        <v>-12.74911307576505</v>
+        <v>-10.36610951211053</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.32317836763835</v>
       </c>
       <c r="E66">
-        <v>-19.04776454572482</v>
+        <v>-19.61019648900347</v>
       </c>
       <c r="F66">
-        <v>-3.671231699305803</v>
+        <v>-3.557676610627838</v>
       </c>
       <c r="G66">
-        <v>-12.57450943292232</v>
+        <v>-11.33822061741942</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.41167858571726</v>
       </c>
       <c r="E67">
-        <v>-18.71621232125323</v>
+        <v>-19.42633138734404</v>
       </c>
       <c r="F67">
-        <v>-3.719142813148921</v>
+        <v>-3.553423772381866</v>
       </c>
       <c r="G67">
-        <v>-12.95296552758867</v>
+        <v>-12.06010904782661</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.49669039356741</v>
       </c>
       <c r="E68">
-        <v>-18.66524434629691</v>
+        <v>-18.52661417150009</v>
       </c>
       <c r="F68">
-        <v>-3.589244035613722</v>
+        <v>-3.773932689904886</v>
       </c>
       <c r="G68">
-        <v>-13.07293026902353</v>
+        <v>-10.78863569354179</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.56898112204259</v>
       </c>
       <c r="E69">
-        <v>-18.70758104979462</v>
+        <v>-17.5186528414508</v>
       </c>
       <c r="F69">
-        <v>-3.836836425371272</v>
+        <v>-3.585899088041218</v>
       </c>
       <c r="G69">
-        <v>-12.71323291801252</v>
+        <v>-11.64602873068937</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.63983745546176</v>
       </c>
       <c r="E70">
-        <v>-18.04957113411007</v>
+        <v>-17.28831653952466</v>
       </c>
       <c r="F70">
-        <v>-3.651554660019704</v>
+        <v>-4.44291143562953</v>
       </c>
       <c r="G70">
-        <v>-12.37547381434796</v>
+        <v>-11.33470314790769</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.70455176607649</v>
       </c>
       <c r="E71">
-        <v>-18.95672410427462</v>
+        <v>-17.77319836542195</v>
       </c>
       <c r="F71">
-        <v>-3.596000200150955</v>
+        <v>-3.81243603515441</v>
       </c>
       <c r="G71">
-        <v>-12.70612907333633</v>
+        <v>-11.11923189054208</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.76373484507866</v>
       </c>
       <c r="E72">
-        <v>-18.769797754186</v>
+        <v>-17.99676912718064</v>
       </c>
       <c r="F72">
-        <v>-4.090379806550533</v>
+        <v>-3.824539311276713</v>
       </c>
       <c r="G72">
-        <v>-12.81472110084615</v>
+        <v>-11.51875014639851</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.81813295635482</v>
       </c>
       <c r="E73">
-        <v>-19.14597809000318</v>
+        <v>-19.63893418505615</v>
       </c>
       <c r="F73">
-        <v>-3.890306712854577</v>
+        <v>-3.769394064904947</v>
       </c>
       <c r="G73">
-        <v>-12.55670552474077</v>
+        <v>-10.88777780296041</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.85889839085785</v>
       </c>
       <c r="E74">
-        <v>-19.11633469914896</v>
+        <v>-18.78606403282155</v>
       </c>
       <c r="F74">
-        <v>-3.772918768203859</v>
+        <v>-3.973374567639909</v>
       </c>
       <c r="G74">
-        <v>-12.7088656121169</v>
+        <v>-11.40800891876725</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.89332808603037</v>
       </c>
       <c r="E75">
-        <v>-19.60032894414076</v>
+        <v>-18.10320185178291</v>
       </c>
       <c r="F75">
-        <v>-4.113873962828733</v>
+        <v>-4.19090716108467</v>
       </c>
       <c r="G75">
-        <v>-12.76531574782559</v>
+        <v>-11.1201768823512</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.9049173365216</v>
       </c>
       <c r="E76">
-        <v>-19.53707521920162</v>
+        <v>-18.76760144429228</v>
       </c>
       <c r="F76">
-        <v>-4.1038333215394</v>
+        <v>-4.658352401382222</v>
       </c>
       <c r="G76">
-        <v>-12.04365044048444</v>
+        <v>-10.22446573983242</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.90491896706459</v>
       </c>
       <c r="E77">
-        <v>-19.96446353909753</v>
+        <v>-19.73440800255986</v>
       </c>
       <c r="F77">
-        <v>-3.918548242718221</v>
+        <v>-4.053378291402285</v>
       </c>
       <c r="G77">
-        <v>-12.29736761634694</v>
+        <v>-9.541344942150065</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.87835848339295</v>
       </c>
       <c r="E78">
-        <v>-19.57698466063122</v>
+        <v>-19.88427784984371</v>
       </c>
       <c r="F78">
-        <v>-4.229035255900726</v>
+        <v>-4.243075255010774</v>
       </c>
       <c r="G78">
-        <v>-12.21774877520702</v>
+        <v>-10.46406053810307</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.83364054127231</v>
       </c>
       <c r="E79">
-        <v>-20.35922873224219</v>
+        <v>-20.50254587763694</v>
       </c>
       <c r="F79">
-        <v>-4.291142930293021</v>
+        <v>-4.532235121040804</v>
       </c>
       <c r="G79">
-        <v>-12.28448882172612</v>
+        <v>-10.18787027577993</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.76408908752177</v>
       </c>
       <c r="E80">
-        <v>-20.91439247473853</v>
+        <v>-20.25310847234644</v>
       </c>
       <c r="F80">
-        <v>-4.410711137947907</v>
+        <v>-4.379867706072071</v>
       </c>
       <c r="G80">
-        <v>-11.67921172432003</v>
+        <v>-9.987167796653377</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.67294067352706</v>
       </c>
       <c r="E81">
-        <v>-21.52877960030718</v>
+        <v>-20.90065308459926</v>
       </c>
       <c r="F81">
-        <v>-4.220859269635095</v>
+        <v>-5.518266519982542</v>
       </c>
       <c r="G81">
-        <v>-11.75659605357798</v>
+        <v>-10.14164442645048</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.56441139501296</v>
       </c>
       <c r="E82">
-        <v>-21.97041449943122</v>
+        <v>-21.0296194958637</v>
       </c>
       <c r="F82">
-        <v>-4.3514406219102</v>
+        <v>-4.97557155644728</v>
       </c>
       <c r="G82">
-        <v>-11.43732007095777</v>
+        <v>-9.833357254832848</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.43595433602107</v>
       </c>
       <c r="E83">
-        <v>-22.33509251126892</v>
+        <v>-22.25197689933213</v>
       </c>
       <c r="F83">
-        <v>-4.659714237392425</v>
+        <v>-4.71196516805881</v>
       </c>
       <c r="G83">
-        <v>-11.33590735622001</v>
+        <v>-10.30068851665832</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.30234484432286</v>
       </c>
       <c r="E84">
-        <v>-23.36826838459292</v>
+        <v>-22.73134304388809</v>
       </c>
       <c r="F84">
-        <v>-4.643096358924864</v>
+        <v>-4.508510678624626</v>
       </c>
       <c r="G84">
-        <v>-11.00326695818818</v>
+        <v>-9.164335866191426</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.15649336636661</v>
       </c>
       <c r="E85">
-        <v>-24.86669514899096</v>
+        <v>-23.89439102327807</v>
       </c>
       <c r="F85">
-        <v>-4.610816537972573</v>
+        <v>-4.87489840925025</v>
       </c>
       <c r="G85">
-        <v>-11.37017643418685</v>
+        <v>-8.247119597572048</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.02183842687814</v>
       </c>
       <c r="E86">
-        <v>-25.22405061835825</v>
+        <v>-25.40677454456775</v>
       </c>
       <c r="F86">
-        <v>-4.685004294199894</v>
+        <v>-4.960761175652627</v>
       </c>
       <c r="G86">
-        <v>-11.12803212676451</v>
+        <v>-9.43571585770842</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.892332579837319</v>
       </c>
       <c r="E87">
-        <v>-26.16966844674394</v>
+        <v>-27.27955666975788</v>
       </c>
       <c r="F87">
-        <v>-4.946167827117508</v>
+        <v>-4.538971404760369</v>
       </c>
       <c r="G87">
-        <v>-11.07885317803155</v>
+        <v>-9.971211216209799</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.787998123876879</v>
       </c>
       <c r="E88">
-        <v>-27.27046349395048</v>
+        <v>-27.99496499348965</v>
       </c>
       <c r="F88">
-        <v>-4.870789706932364</v>
+        <v>-4.958182467927712</v>
       </c>
       <c r="G88">
-        <v>-10.81868512058318</v>
+        <v>-9.353570475967722</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.711211809221124</v>
       </c>
       <c r="E89">
-        <v>-29.25467777904735</v>
+        <v>-28.57816451856747</v>
       </c>
       <c r="F89">
-        <v>-4.918684253427426</v>
+        <v>-5.611667429750395</v>
       </c>
       <c r="G89">
-        <v>-11.15513829806708</v>
+        <v>-10.15289245395625</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.674631725358307</v>
       </c>
       <c r="E90">
-        <v>-29.99121596249891</v>
+        <v>-29.99502214490235</v>
       </c>
       <c r="F90">
-        <v>-5.003006256460596</v>
+        <v>-5.934317361508205</v>
       </c>
       <c r="G90">
-        <v>-10.96246824931805</v>
+        <v>-8.789518646234496</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.689457394491551</v>
       </c>
       <c r="E91">
-        <v>-31.09059133310404</v>
+        <v>-31.22048834577706</v>
       </c>
       <c r="F91">
-        <v>-5.07704987675983</v>
+        <v>-5.453281097232921</v>
       </c>
       <c r="G91">
-        <v>-11.07034497052791</v>
+        <v>-8.858273362791103</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.758640641228929</v>
       </c>
       <c r="E92">
-        <v>-33.16912693906967</v>
+        <v>-33.70220757806761</v>
       </c>
       <c r="F92">
-        <v>-5.330467346093866</v>
+        <v>-5.373539137569829</v>
       </c>
       <c r="G92">
-        <v>-11.43537758779458</v>
+        <v>-10.76931586099977</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.900435403048593</v>
       </c>
       <c r="E93">
-        <v>-34.75163388036813</v>
+        <v>-35.96970734742531</v>
       </c>
       <c r="F93">
-        <v>-5.081589330127171</v>
+        <v>-5.95172964431505</v>
       </c>
       <c r="G93">
-        <v>-11.54309024792647</v>
+        <v>-9.526471164821102</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.10423794921747</v>
       </c>
       <c r="E94">
-        <v>-36.3484915557969</v>
+        <v>-36.73860827037268</v>
       </c>
       <c r="F94">
-        <v>-5.185478199581868</v>
+        <v>-5.827990606787068</v>
       </c>
       <c r="G94">
-        <v>-11.45337836926969</v>
+        <v>-9.711095658306379</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.38727097153848</v>
       </c>
       <c r="E95">
-        <v>-37.84361479840635</v>
+        <v>-39.45058229205724</v>
       </c>
       <c r="F95">
-        <v>-5.237326543690492</v>
+        <v>-6.453905016342375</v>
       </c>
       <c r="G95">
-        <v>-11.56079571946123</v>
+        <v>-10.92204688092725</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.73646309120919</v>
       </c>
       <c r="E96">
-        <v>-40.16009454263101</v>
+        <v>-41.18721131773275</v>
       </c>
       <c r="F96">
-        <v>-5.256789864186669</v>
+        <v>-5.78101720484392</v>
       </c>
       <c r="G96">
-        <v>-11.97610649468327</v>
+        <v>-10.92606965855913</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.15320351353793</v>
       </c>
       <c r="E97">
-        <v>-42.83916920064985</v>
+        <v>-43.72091969586837</v>
       </c>
       <c r="F97">
-        <v>-5.297633347349102</v>
+        <v>-5.689735258892428</v>
       </c>
       <c r="G97">
-        <v>-12.24802132531445</v>
+        <v>-10.81915761648774</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.63591384103904</v>
       </c>
       <c r="E98">
-        <v>-44.5156034855784</v>
+        <v>-46.06665791065659</v>
       </c>
       <c r="F98">
-        <v>-5.161437320817821</v>
+        <v>-5.917700311408047</v>
       </c>
       <c r="G98">
-        <v>-12.08104980381899</v>
+        <v>-10.65942118853085</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.15827843325973</v>
       </c>
       <c r="E99">
-        <v>-46.49028533288913</v>
+        <v>-47.54054713864407</v>
       </c>
       <c r="F99">
-        <v>-5.422633160064144</v>
+        <v>-6.339769242115048</v>
       </c>
       <c r="G99">
-        <v>-12.77017851817669</v>
+        <v>-11.24392159102254</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.7456560115551</v>
       </c>
       <c r="E100">
-        <v>-48.69055198077346</v>
+        <v>-48.87126413240505</v>
       </c>
       <c r="F100">
-        <v>-5.377591510904324</v>
+        <v>-5.742761541447833</v>
       </c>
       <c r="G100">
-        <v>-13.08425048340361</v>
+        <v>-11.5745932561187</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.32608447078183</v>
       </c>
       <c r="E101">
-        <v>-50.1233804028149</v>
+        <v>-52.28082240412718</v>
       </c>
       <c r="F101">
-        <v>-5.731893361123103</v>
+        <v>-6.00817791261142</v>
       </c>
       <c r="G101">
-        <v>-13.40194491723217</v>
+        <v>-12.04610151298934</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.99224134850874</v>
       </c>
       <c r="E102">
-        <v>-52.56426978133378</v>
+        <v>-53.22483941695116</v>
       </c>
       <c r="F102">
-        <v>-5.615711519410862</v>
+        <v>-6.361016037629453</v>
       </c>
       <c r="G102">
-        <v>-13.34524540868497</v>
+        <v>-12.27120643685349</v>
       </c>
     </row>
   </sheetData>
